--- a/insurance_data.xlsx
+++ b/insurance_data.xlsx
@@ -1612,21 +1612,21 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>RANJEET SOLANKI</t>
+          <t>CHIRAG JOSHI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AAREEN</t>
+          <t>DINESH RACHH</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>6103133141 - 01</t>
+          <t>7102835188</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MOTOR INSURANCE</t>
+          <t>TRAVEL INSURANCE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1646,63 +1646,52 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>20/12/2025</t>
+          <t>25/12/2025</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>19/12/2026</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>05/12/2025</t>
+          <t>08/12/2025</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>RENEWAL</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SAMEER SHAH</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>RANJEET SOLANKI</t>
+          <t>CHIRAG JOSHI</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>MH 02 GD 2435(E.BULLET)</t>
+          <t>TRAVEL</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>122153</v>
+        <v>500000</v>
       </c>
       <c r="P8" t="n">
-        <v>1149.86</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>296.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0</v>
+        <v>5786</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
-        <v>1707</v>
+        <v>5786</v>
       </c>
       <c r="U8" t="n">
         <v>15</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>172.48</t>
+          <t>867.90</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -1712,7 +1701,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1722,52 +1711,52 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Aaren Solanki.pdf</t>
+          <t>Dinesh Rachh-Travel.pdf</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1u6ElaMGt-1ypniWNFppNSVWlLwVIG-4O</t>
+          <t>1a_bVrnWK8wd7EfeiVYUb8sWO3MlXpI3D</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>RS01/AAREEN/RS01 - AAREEN - Aaren Solanki.pdf</t>
+          <t>CJ01/DINESH RACHH/CJ01 - DINESH RACHH - Dinesh Rachh-Travel.pdf</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1u6ElaMGt-1ypniWNFppNSVWlLwVIG-4O/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1a_bVrnWK8wd7EfeiVYUb8sWO3MlXpI3D/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>2025-12-08T09:42:08.836989+00:00</t>
+          <t>2025-12-08T08:06:20.222658+00:00</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-08T09:42:08.836989+00:00</t>
+          <t>2025-12-08T08:06:20.222658+00:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ALPESH MEHTA </t>
+          <t>RANJEET SOLANKI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ALPESH MEHTA</t>
+          <t>AAREEN</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0238878953-05</t>
+          <t>6103133141 - 01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1777,7 +1766,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>HEALTH INSURANCE</t>
+          <t>MOTOR INSURANCE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1787,12 +1776,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>20/12/2025</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11/12/2026</t>
+          <t>19/12/2026</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1812,29 +1801,38 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t xml:space="preserve">MEENA FASHIONS </t>
+          <t>RANJEET SOLANKI</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>HEALTH</t>
-        </is>
+          <t>MH 02 GD 2435(E.BULLET)</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>122153</v>
       </c>
       <c r="P9" t="n">
-        <v>86949</v>
+        <v>1149.86</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>296.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T9" t="n">
-        <v>86949</v>
+        <v>1707</v>
       </c>
       <c r="U9" t="n">
         <v>15</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>13042.35</t>
+          <t>172.48</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -1849,70 +1847,43 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>858187</t>
+          <t>ONLINE</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Alpesh Mehta(Medicare).pdf</t>
+          <t>Aaren Solanki.pdf</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1shnNJnhoMVZBxWVPrDTZ-_S6p5U-bgK_</t>
+          <t>1u6ElaMGt-1ypniWNFppNSVWlLwVIG-4O</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>AM01/ALPESH MEHTA/AM01 - ALPESH MEHTA - Alpesh Mehta(Medicare).pdf</t>
+          <t>RS01/AAREEN/RS01 - AAREEN - Aaren Solanki.pdf</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1shnNJnhoMVZBxWVPrDTZ-_S6p5U-bgK_/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1u6ElaMGt-1ypniWNFppNSVWlLwVIG-4O/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>2025-12-08T10:19:21.182285+00:00</t>
+          <t>2025-12-08T09:42:08.836989+00:00</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-08T10:19:21.182285+00:00</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>INDIVIDUAL</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>ALPESH MEHTA</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>NIPA MEHTA</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0</v>
+          <t>2025-12-08T09:42:08.836989+00:00</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1926,7 +1897,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>7041024408-01</t>
+          <t>0238878953-05</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1946,12 +1917,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>12/12/2025</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>08/12/2026</t>
+          <t>11/12/2026</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1976,24 +1947,24 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>TOP-UP</t>
+          <t>HEALTH</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>13783</v>
+        <v>86949</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>13783</v>
+        <v>86949</v>
       </c>
       <c r="U10" t="n">
         <v>15</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2067.45</t>
+          <t>13042.35</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -2008,78 +1979,84 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>858186</t>
+          <t>858187</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Alpesh Mehta(Medicareplus).pdf</t>
+          <t>Alpesh Mehta(Medicare).pdf</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1uESnM9i-mjiGJxu40smQUPHFIHE8B6kf</t>
+          <t>1shnNJnhoMVZBxWVPrDTZ-_S6p5U-bgK_</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>AM01/ALPESH MEHTA/AM01 - ALPESH MEHTA - Alpesh Mehta(Medicareplus).pdf</t>
+          <t>AM01/ALPESH MEHTA/AM01 - ALPESH MEHTA - Alpesh Mehta(Medicare).pdf</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1uESnM9i-mjiGJxu40smQUPHFIHE8B6kf/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1shnNJnhoMVZBxWVPrDTZ-_S6p5U-bgK_/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>2025-12-08T10:43:13.132921+00:00</t>
+          <t>2025-12-08T10:19:21.182285+00:00</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-08T10:43:13.132921+00:00</t>
+          <t>2025-12-08T10:19:21.182285+00:00</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>FLOATER</t>
-        </is>
-      </c>
-      <c r="AI10" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>5000000</v>
+          <t>INDIVIDUAL</t>
+        </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
           <t>ALPESH MEHTA</t>
         </is>
       </c>
+      <c r="AM10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
       <c r="AP10" t="inlineStr">
         <is>
           <t>NIPA MEHTA</t>
         </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>HARSHAD HEMANI</t>
+          <t xml:space="preserve">ALPESH MEHTA </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HARSHAD HEMANI</t>
+          <t>ALPESH MEHTA</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>6205577380 00 00</t>
+          <t>7041024408-01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2089,7 +2066,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>MOTOR INSURANCE</t>
+          <t>HEALTH INSURANCE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2099,19 +2076,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>09/12/2025</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>08/12/2026</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>05/12/2025</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>04/12/2026</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>05/12/2025</t>
-        </is>
-      </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>RENEWAL</t>
@@ -2124,38 +2101,29 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>HEMANI</t>
+          <t xml:space="preserve">MEENA FASHIONS </t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>MH-01-EB-9701(M.CIAZ)</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>647361</v>
+          <t>TOP-UP</t>
+        </is>
       </c>
       <c r="P11" t="n">
-        <v>2072.15</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>7323.35</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3841</v>
+        <v>13783</v>
       </c>
       <c r="S11" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>15619</v>
+        <v>13783</v>
       </c>
       <c r="U11" t="n">
         <v>15</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>310.82</t>
+          <t>2067.45</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -2170,87 +2138,108 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>ONLINE</t>
+          <t>858186</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Apoorva Hemani(Ciaz9701).pdf</t>
+          <t>Alpesh Mehta(Medicareplus).pdf</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1fxmhEy5XEmUgrjeetI9N2MfQ9EDIyimx</t>
+          <t>1uESnM9i-mjiGJxu40smQUPHFIHE8B6kf</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>HH01/HARSHAD HEMANI/HH01 - HARSHAD HEMANI - Apoorva Hemani(Ciaz9701).pdf</t>
+          <t>AM01/ALPESH MEHTA/AM01 - ALPESH MEHTA - Alpesh Mehta(Medicareplus).pdf</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1fxmhEy5XEmUgrjeetI9N2MfQ9EDIyimx/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1uESnM9i-mjiGJxu40smQUPHFIHE8B6kf/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>2025-12-08T11:14:35.621635+00:00</t>
+          <t>2025-12-08T10:43:13.132921+00:00</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-08T11:14:35.621635+00:00</t>
+          <t>2025-12-08T10:43:13.132921+00:00</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>FLOATER</t>
+        </is>
+      </c>
+      <c r="AI11" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>ALPESH MEHTA</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>NIPA MEHTA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BABU NICHANI</t>
+          <t>HARSHAD HEMANI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BABU NICHANI</t>
+          <t>HARSHAD HEMANI</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>132700/48/2026/6723</t>
+          <t>6205577380 00 00</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>The Oriental Insurance Co Ltd</t>
+          <t>Tata AIG General Insurance Co Ltd</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>HEALTH INSURANCE</t>
+          <t>MOTOR INSURANCE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jaimini Thakkar</t>
+          <t>Sweta Shah</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>04/12/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>03/12/2026</t>
+          <t>04/12/2026</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -2263,26 +2252,40 @@
           <t>SAMEER SHAH</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>HEMANI</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>HEALTH</t>
-        </is>
+          <t>MH-01-EB-9701(M.CIAZ)</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>647361</v>
       </c>
       <c r="P12" t="n">
-        <v>61517</v>
+        <v>2072.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>7323.35</v>
+      </c>
+      <c r="R12" t="n">
+        <v>3841</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="T12" t="n">
-        <v>61517</v>
+        <v>15619</v>
       </c>
       <c r="U12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>6151.70</t>
+          <t>310.82</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -2302,78 +2305,57 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Babu Nichani(HEALTH).pdf</t>
+          <t>Apoorva Hemani(Ciaz9701).pdf</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1m9FMcspBxTpxPJpGblFsGF_Red6gmEX-</t>
+          <t>1fxmhEy5XEmUgrjeetI9N2MfQ9EDIyimx</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>BN01/BABU NICHANI/BN01 - BABU NICHANI - Babu Nichani(HEALTH).pdf</t>
+          <t>HH01/HARSHAD HEMANI/HH01 - HARSHAD HEMANI - Apoorva Hemani(Ciaz9701).pdf</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1m9FMcspBxTpxPJpGblFsGF_Red6gmEX-/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1fxmhEy5XEmUgrjeetI9N2MfQ9EDIyimx/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.417666+00:00</t>
+          <t>2025-12-08T11:14:35.621635+00:00</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-12-08T11:31:59.417666+00:00</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>INDIVIDUAL</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>BABU NICHANI</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>450000</v>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>LLEENA NICHANI</t>
-        </is>
-      </c>
-      <c r="AQ12" t="n">
-        <v>450000</v>
+          <t>2025-12-08T11:14:35.621635+00:00</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>KETAN GALA</t>
+          <t>BABU NICHANI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KUNTI GALA</t>
+          <t>BABU NICHANI</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12-8457-0000053226-01</t>
+          <t>132700/48/2026/6723</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Bajaj General Insurance Limited</t>
+          <t>The Oriental Insurance Co Ltd</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2383,22 +2365,22 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sameer Shah</t>
+          <t>Jaimini Thakkar</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>03/12/2025</t>
+          <t>04/12/2025</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>02/12/2026</t>
+          <t>03/12/2026</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>02/12/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2417,20 +2399,20 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>88413</v>
+        <v>61517</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>88413</v>
+        <v>61517</v>
       </c>
       <c r="U13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>13261.95</t>
+          <t>6151.70</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -2450,78 +2432,78 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Kunti Gala(MHCF).pdf</t>
+          <t>Babu Nichani(HEALTH).pdf</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>1D4c9zQYzrRFYiLSU-sQHMwIR6HmQopEc</t>
+          <t>1m9FMcspBxTpxPJpGblFsGF_Red6gmEX-</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>KG01/KUNTI GALA/KG01 - KUNTI GALA - Kunti Gala(MHCF).pdf</t>
+          <t>BN01/BABU NICHANI/BN01 - BABU NICHANI - Babu Nichani(HEALTH).pdf</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1D4c9zQYzrRFYiLSU-sQHMwIR6HmQopEc/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1m9FMcspBxTpxPJpGblFsGF_Red6gmEX-/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>2025-12-09T06:51:04.871086+00:00</t>
+          <t>2025-12-08T11:31:59.417666+00:00</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>2025-12-09T06:51:04.871086+00:00</t>
+          <t>2025-12-08T11:31:59.417666+00:00</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>FLOATER</t>
-        </is>
-      </c>
-      <c r="AI13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>5000000</v>
+          <t>INDIVIDUAL</t>
+        </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>KETAN GALA</t>
-        </is>
+          <t>BABU NICHANI</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>450000</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>KUNTI GALA</t>
-        </is>
+          <t>LLEENA NICHANI</t>
+        </is>
+      </c>
+      <c r="AQ13" t="n">
+        <v>450000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAURANG TALATI </t>
+          <t>KETAN GALA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">GAURANG TALATI </t>
+          <t>KUNTI GALA</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>7000190288</t>
+          <t>12-8457-0000053226-01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Tata AIG General Insurance Co Ltd</t>
+          <t>Bajaj General Insurance Limited</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2531,22 +2513,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sweta Shah</t>
+          <t>Sameer Shah</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>07/12/2025</t>
+          <t>03/12/2025</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>06/12/2026</t>
+          <t>02/12/2026</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>06/12/2025</t>
+          <t>02/12/2025</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2565,20 +2547,20 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>31871</v>
+        <v>88413</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>31871</v>
+        <v>88413</v>
       </c>
       <c r="U14" t="n">
         <v>15</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>4780.65</t>
+          <t>13261.95</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -2598,32 +2580,32 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Gaurang Talati.pdf</t>
+          <t>Kunti Gala(MHCF).pdf</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>1CAfS0VkEhUMVjGaJUf80V_Y6SGR4BD9Q</t>
+          <t>1D4c9zQYzrRFYiLSU-sQHMwIR6HmQopEc</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>GT01/GAURANG TALATI /GT01 - GAURANG TALATI  - Gaurang Talati.pdf</t>
+          <t>KG01/KUNTI GALA/KG01 - KUNTI GALA - Kunti Gala(MHCF).pdf</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1CAfS0VkEhUMVjGaJUf80V_Y6SGR4BD9Q/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1D4c9zQYzrRFYiLSU-sQHMwIR6HmQopEc/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>2025-12-09T06:24:07.253308+00:00</t>
+          <t>2025-12-09T06:51:04.871086+00:00</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>2025-12-09T06:24:07.253308+00:00</t>
+          <t>2025-12-09T06:51:04.871086+00:00</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
@@ -2632,39 +2614,44 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000000</v>
+        <v>5000000</v>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>GAURANG TALATI</t>
+          <t>KETAN GALA</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>KUNTI GALA</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JOJE JOSEPH</t>
+          <t xml:space="preserve">GAURANG TALATI </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>JOJE JOSEPH</t>
+          <t xml:space="preserve">GAURANG TALATI </t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>12-8457-0000054318-01</t>
+          <t>7000190288</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bajaj General Insurance Limited</t>
+          <t>Tata AIG General Insurance Co Ltd</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -2674,22 +2661,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sameer Shah</t>
+          <t>Sweta Shah</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>09/12/2025</t>
+          <t>07/12/2025</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>08/12/2026</t>
+          <t>06/12/2026</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>08/12/2025</t>
+          <t>06/12/2025</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2708,20 +2695,20 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>66620</v>
+        <v>31871</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>66620</v>
+        <v>31871</v>
       </c>
       <c r="U15" t="n">
         <v>15</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>9993.00</t>
+          <t>4780.65</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -2741,32 +2728,32 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Joje Joseph.pdf</t>
+          <t>Gaurang Talati.pdf</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>1LRfA_KwOxS0Mwm-aGCcPfq1kZccMsVKP</t>
+          <t>1CAfS0VkEhUMVjGaJUf80V_Y6SGR4BD9Q</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>JJ01/JOJE JOSEPH/JJ01 - JOJE JOSEPH - Joje Joseph.pdf</t>
+          <t>GT01/GAURANG TALATI /GT01 - GAURANG TALATI  - Gaurang Talati.pdf</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1LRfA_KwOxS0Mwm-aGCcPfq1kZccMsVKP/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1CAfS0VkEhUMVjGaJUf80V_Y6SGR4BD9Q/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>2025-12-09T07:34:18.546621+00:00</t>
+          <t>2025-12-09T06:24:07.253308+00:00</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>2025-12-09T07:34:18.546621+00:00</t>
+          <t>2025-12-09T06:24:07.253308+00:00</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
@@ -2775,74 +2762,59 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>2000000</v>
+        <v>1000000</v>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>JOJE JOSEPH</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>SHIJI JOSEPH</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>SHAUN JOSEPHH</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>REBECCA JOSEPH</t>
+          <t>GAURANG TALATI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ADIYERI  SUNIL</t>
+          <t>JOJE JOSEPH</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ADIYERI  SUNIL</t>
+          <t>JOJE JOSEPH</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">0156588457 </t>
+          <t>12-8457-0000054318-01</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tata AIG General Insurance Co Ltd</t>
+          <t>Bajaj General Insurance Limited</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MOTOR INSURANCE</t>
+          <t>HEALTH INSURANCE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sweta Shah</t>
+          <t>Sameer Shah</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>23/12/2025</t>
+          <t>09/12/2025</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>22/12/2026</t>
+          <t>08/12/2026</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2862,33 +2834,24 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MH-02-EE-0137(NISSAN)</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>383700</v>
+          <t>HEALTH</t>
+        </is>
       </c>
       <c r="P16" t="n">
-        <v>1322.62</v>
-      </c>
-      <c r="Q16" t="n">
+        <v>66620</v>
+      </c>
+      <c r="S16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>3916</v>
-      </c>
-      <c r="S16" t="n">
-        <v>18</v>
-      </c>
       <c r="T16" t="n">
-        <v>6182</v>
+        <v>66620</v>
       </c>
       <c r="U16" t="n">
         <v>15</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>198.39</t>
+          <t>9993.00</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -2901,54 +2864,90 @@
           <t>No</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>ONLINE</t>
+        </is>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>Adiyeri Sunil.pdf</t>
+          <t>Joje Joseph.pdf</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>1Xx_YnxMpf7_O5jFo6W0fYosg2u30uAxX</t>
+          <t>1LRfA_KwOxS0Mwm-aGCcPfq1kZccMsVKP</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>AD01/ADIYERI  SUNIL/AD01 - ADIYERI  SUNIL - Adiyeri Sunil.pdf</t>
+          <t>JJ01/JOJE JOSEPH/JJ01 - JOJE JOSEPH - Joje Joseph.pdf</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1Xx_YnxMpf7_O5jFo6W0fYosg2u30uAxX/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1LRfA_KwOxS0Mwm-aGCcPfq1kZccMsVKP/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>2025-12-09T07:57:06.058291+00:00</t>
+          <t>2025-12-09T07:34:18.546621+00:00</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>2025-12-09T07:57:06.058291+00:00</t>
+          <t>2025-12-09T07:34:18.546621+00:00</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>FLOATER</t>
+        </is>
+      </c>
+      <c r="AI16" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>JOJE JOSEPH</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>SHIJI JOSEPH</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>SHAUN JOSEPHH</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>REBECCA JOSEPH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CHIRAG JOSHI</t>
+          <t>ADIYERI  SUNIL</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DINESH RACHH</t>
+          <t>ADIYERI  SUNIL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7102835188</t>
+          <t xml:space="preserve">0156588457 </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2958,7 +2957,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TRAVEL INSURANCE</t>
+          <t>MOTOR INSURANCE</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2968,12 +2967,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>25/12/2025</t>
+          <t>23/12/2025</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>12/12/2025</t>
+          <t>22/12/2026</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2983,37 +2982,43 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>RENEWAL</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CHIRAG JOSHI</t>
+          <t>SAMEER SHAH</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>TRAVEL</t>
+          <t>MH-02-EE-0137(NISSAN)</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>500000</v>
+        <v>383700</v>
       </c>
       <c r="P17" t="n">
-        <v>5786</v>
+        <v>1322.62</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>3916</v>
       </c>
       <c r="S17" t="n">
         <v>18</v>
       </c>
       <c r="T17" t="n">
-        <v>5786</v>
+        <v>6182</v>
       </c>
       <c r="U17" t="n">
         <v>15</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>867.90</t>
+          <t>198.39</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -3023,42 +3028,37 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>ONLINE</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>Dinesh Rachh-Travel.pdf</t>
+          <t>Adiyeri Sunil.pdf</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1a_bVrnWK8wd7EfeiVYUb8sWO3MlXpI3D</t>
+          <t>1Xx_YnxMpf7_O5jFo6W0fYosg2u30uAxX</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>CJ01/DINESH RACHH/CJ01 - DINESH RACHH - Dinesh Rachh-Travel.pdf</t>
+          <t>AD01/ADIYERI  SUNIL/AD01 - ADIYERI  SUNIL - Adiyeri Sunil.pdf</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>https://drive.google.com/file/d/1a_bVrnWK8wd7EfeiVYUb8sWO3MlXpI3D/view?usp=drivesdk</t>
+          <t>https://drive.google.com/file/d/1Xx_YnxMpf7_O5jFo6W0fYosg2u30uAxX/view?usp=drivesdk</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>2025-12-08T08:06:20.222658+00:00</t>
+          <t>2025-12-09T07:57:06.058291+00:00</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>2025-12-08T08:06:20.222658+00:00</t>
+          <t>2025-12-09T07:57:06.058291+00:00</t>
         </is>
       </c>
     </row>
